--- a/src/test/resources/data/Regression_TestData.xlsx
+++ b/src/test/resources/data/Regression_TestData.xlsx
@@ -8,7 +8,8 @@
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="CheckoutTests" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="LoginTests" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="CheckoutTests" sheetId="2" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -20,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="21">
   <si>
     <t xml:space="preserve">Sl.No.</t>
   </si>
@@ -34,6 +35,21 @@
     <t xml:space="preserve">Password</t>
   </si>
   <si>
+    <t xml:space="preserve">Login-001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">standard_user</t>
+  </si>
+  <si>
+    <t xml:space="preserve">secret_sauce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Login-002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">locked_out_user</t>
+  </si>
+  <si>
     <t xml:space="preserve">ProductName</t>
   </si>
   <si>
@@ -47,12 +63,6 @@
   </si>
   <si>
     <t xml:space="preserve">Checkout-001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">standard_user</t>
-  </si>
-  <si>
-    <t xml:space="preserve">secret_sauce</t>
   </si>
   <si>
     <t xml:space="preserve">Sauce Labs Bike Light</t>
@@ -170,16 +180,20 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -306,93 +320,160 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="A1:D3"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="9.95"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="14.47"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="11.03"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPage &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="A1:H3"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="13.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="6"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="12.48"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="11.03"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="37.02"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="9.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="8.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="7.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="6"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="12.48"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="11.03"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="37.02"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="9.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="8.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="7.83"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
+      <c r="E1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="D2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="H2" s="2" t="n">
+      <c r="E2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" s="3" t="n">
         <v>560023</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="n">
+      <c r="A3" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="G3" s="2" t="s">
+      <c r="B3" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="H3" s="2" t="n">
+      <c r="C3" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="H3" s="3" t="n">
         <v>560017</v>
       </c>
     </row>
